--- a/data/performance/daily/signal_list_2026-05-24.xlsx
+++ b/data/performance/daily/signal_list_2026-05-24.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 41.7%  (5W / 7L of 12 evaluated)</t>
+          <t>Win Rate: 66.7%  (8W / 4L of 12 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="D5" t="n">
         <v>2400</v>
@@ -553,14 +553,14 @@
         <v>2500</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4.17</v>
+        <v>5.04</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="D6" t="n">
         <v>2300</v>
@@ -595,12 +595,12 @@
         <v>2350</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+        <v>-0.86</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="D7" t="n">
         <v>1495</v>
@@ -637,12 +637,12 @@
         <v>1505</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+        <v>-0.66</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -684,7 +684,7 @@
       <c r="G8" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
         <v>75</v>
@@ -721,14 +721,14 @@
         <v>75</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>860</v>
+        <v>780</v>
       </c>
       <c r="D10" t="n">
         <v>975</v>
@@ -763,12 +763,12 @@
         <v>975</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13.37</v>
+        <v>25</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -810,7 +810,7 @@
       <c r="G11" s="4" t="n">
         <v>3.6</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -852,7 +852,7 @@
       <c r="G12" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D13" t="n">
         <v>234</v>
@@ -889,12 +889,12 @@
         <v>240</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.35</v>
+        <v>5.26</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+        <v>2.63</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -936,7 +936,7 @@
       <c r="G14" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -978,7 +978,7 @@
       <c r="G15" s="4" t="n">
         <v>9.93</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D16" t="n">
         <v>496</v>
@@ -1015,14 +1015,14 @@
         <v>525</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8</v>
+        <v>3.33</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
